--- a/data/trans_orig/IQ27-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, referido por progenitor/a</t>
+          <t>Peso medio, en kilogramos, declarado por progenitor/a (tasa de respuesta: 96,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,18; 33,93</t>
+          <t>29,2; 34,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,1; 32,95</t>
+          <t>28,0; 32,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,79; 33,33</t>
+          <t>28,54; 33,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,12; 36,12</t>
+          <t>31,15; 36,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,13; 38,77</t>
+          <t>33,33; 39,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,35; 34,79</t>
+          <t>29,17; 34,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,16; 34,35</t>
+          <t>29,17; 34,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,61; 42,11</t>
+          <t>34,83; 42,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,95; 35,88</t>
+          <t>32,12; 35,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,36; 33,05</t>
+          <t>29,58; 33,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,68; 33,33</t>
+          <t>29,52; 33,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,11; 39,11</t>
+          <t>34,21; 39,38</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,12; 34,88</t>
+          <t>31,3; 35,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,28; 31,11</t>
+          <t>27,42; 31,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,32; 31,9</t>
+          <t>28,38; 31,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,15; 36,15</t>
+          <t>31,05; 36,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,7; 35,77</t>
+          <t>31,82; 35,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,76; 32,78</t>
+          <t>28,65; 32,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,83; 32,55</t>
+          <t>28,83; 32,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,52; 40,54</t>
+          <t>35,5; 40,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,84; 34,76</t>
+          <t>32,05; 34,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,75; 31,46</t>
+          <t>28,53; 31,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,11; 31,71</t>
+          <t>29,1; 31,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,32; 38,03</t>
+          <t>34,5; 38,14</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,09; 33,81</t>
+          <t>28,88; 33,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,27; 31,54</t>
+          <t>27,04; 31,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,6; 31,41</t>
+          <t>27,69; 31,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,4; 46,02</t>
+          <t>33,25; 46,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,86; 36,05</t>
+          <t>30,89; 36,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,18; 31,71</t>
+          <t>27,24; 31,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,24; 32,49</t>
+          <t>28,11; 32,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,93; 43,74</t>
+          <t>35,88; 44,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,72; 34,02</t>
+          <t>30,72; 33,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,87; 31,08</t>
+          <t>27,85; 31,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,46; 31,4</t>
+          <t>28,47; 31,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,04; 43,69</t>
+          <t>35,74; 44,29</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,94; 32,58</t>
+          <t>28,93; 32,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,32; 32,69</t>
+          <t>28,38; 32,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,1; 32,28</t>
+          <t>28,26; 32,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,24; 35,9</t>
+          <t>30,91; 35,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,18; 35,68</t>
+          <t>31,24; 35,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,14; 33,34</t>
+          <t>29,04; 33,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,26; 33,59</t>
+          <t>29,23; 33,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,21; 38,04</t>
+          <t>32,91; 38,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,59; 33,42</t>
+          <t>30,54; 33,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,26; 32,29</t>
+          <t>29,17; 32,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,25; 32,14</t>
+          <t>29,32; 32,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,84; 36,27</t>
+          <t>32,87; 36,2</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,58; 32,7</t>
+          <t>30,74; 32,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,73; 30,91</t>
+          <t>28,72; 30,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,08; 31,15</t>
+          <t>29,07; 31,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,43; 38,48</t>
+          <t>33,25; 39,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,79; 35,17</t>
+          <t>32,83; 35,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,52; 31,89</t>
+          <t>29,67; 32,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,86; 31,96</t>
+          <t>29,94; 32,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,18; 39,47</t>
+          <t>36,38; 39,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,09; 33,71</t>
+          <t>32,11; 33,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,51; 31,15</t>
+          <t>29,54; 31,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,8; 31,25</t>
+          <t>29,82; 31,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,29; 38,41</t>
+          <t>35,32; 38,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Habitat-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,2; 34,08</t>
+          <t>29,41; 34,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,0; 32,75</t>
+          <t>28,24; 32,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,54; 33,41</t>
+          <t>28,56; 33,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,15; 36,62</t>
+          <t>30,98; 36,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,33; 39,06</t>
+          <t>33,16; 38,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,17; 34,87</t>
+          <t>29,57; 34,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,17; 34,35</t>
+          <t>29,11; 34,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,83; 42,1</t>
+          <t>34,73; 42,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32,12; 35,9</t>
+          <t>32,17; 35,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,58; 33,16</t>
+          <t>29,5; 32,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,52; 33,15</t>
+          <t>29,62; 33,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,21; 39,38</t>
+          <t>34,14; 39,03</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,3; 35,27</t>
+          <t>31,23; 35,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,42; 31,15</t>
+          <t>27,4; 31,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,38; 31,89</t>
+          <t>28,18; 31,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,05; 36,12</t>
+          <t>31,36; 36,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,82; 35,68</t>
+          <t>31,49; 35,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,65; 32,62</t>
+          <t>28,79; 33,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,83; 32,72</t>
+          <t>28,84; 32,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,5; 40,54</t>
+          <t>35,58; 40,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,05; 34,91</t>
+          <t>31,91; 34,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,53; 31,34</t>
+          <t>28,66; 31,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,1; 31,7</t>
+          <t>29,02; 31,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,5; 38,14</t>
+          <t>34,25; 37,95</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,88; 33,46</t>
+          <t>29,17; 33,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,04; 31,48</t>
+          <t>27,26; 31,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,69; 31,69</t>
+          <t>27,6; 31,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,25; 46,78</t>
+          <t>33,36; 47,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,89; 36,08</t>
+          <t>30,76; 35,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,24; 31,89</t>
+          <t>27,29; 31,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,11; 32,32</t>
+          <t>28,26; 32,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,88; 44,14</t>
+          <t>35,91; 43,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,72; 33,99</t>
+          <t>30,73; 34,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,85; 31,01</t>
+          <t>27,81; 31,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,47; 31,29</t>
+          <t>28,56; 31,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35,74; 44,29</t>
+          <t>35,89; 43,74</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,93; 32,63</t>
+          <t>28,96; 32,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,38; 32,72</t>
+          <t>28,49; 32,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,26; 32,3</t>
+          <t>28,16; 32,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,91; 35,86</t>
+          <t>31,12; 35,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,24; 35,81</t>
+          <t>31,17; 35,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,04; 33,13</t>
+          <t>29,09; 33,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,23; 33,64</t>
+          <t>29,28; 33,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,91; 38,13</t>
+          <t>33,18; 38,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,54; 33,52</t>
+          <t>30,45; 33,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,17; 32,19</t>
+          <t>29,14; 32,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,32; 32,36</t>
+          <t>29,16; 32,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,87; 36,2</t>
+          <t>32,91; 36,31</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,74; 32,8</t>
+          <t>30,67; 32,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,72; 30,82</t>
+          <t>28,74; 30,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,07; 31,1</t>
+          <t>29,11; 31,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,25; 39,0</t>
+          <t>33,3; 38,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,83; 35,19</t>
+          <t>32,76; 35,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,67; 32,01</t>
+          <t>29,68; 32,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,94; 32,09</t>
+          <t>29,84; 31,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,38; 39,59</t>
+          <t>36,28; 39,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,11; 33,67</t>
+          <t>32,02; 33,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,54; 31,01</t>
+          <t>29,51; 31,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,82; 31,29</t>
+          <t>29,76; 31,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,32; 38,26</t>
+          <t>35,36; 38,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Habitat-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35,91</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31,92</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31,56</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>38,44</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>31,66</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>30,48</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>30,9</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33,68</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>35,91</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,92</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,56</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>38,27</t>
+          <t>34,54</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,23</t>
+          <t>36,58</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,41; 34,27</t>
+          <t>33,13; 38,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,24; 32,83</t>
+          <t>29,35; 34,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,56; 33,39</t>
+          <t>29,16; 34,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,98; 36,1</t>
+          <t>35,23; 41,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,16; 38,7</t>
+          <t>29,18; 33,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,57; 34,56</t>
+          <t>28,1; 32,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,11; 34,63</t>
+          <t>28,79; 33,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,73; 42,47</t>
+          <t>32,03; 37,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32,17; 35,96</t>
+          <t>31,95; 35,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,5; 32,82</t>
+          <t>29,36; 33,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,62; 33,08</t>
+          <t>29,68; 33,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,14; 39,03</t>
+          <t>34,79; 39,04</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33,68</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30,69</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30,71</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38,92</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>33,08</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>29,18</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>30,01</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>33,91</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>33,68</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>30,69</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>30,71</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,79</t>
+          <t>35,58</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,12</t>
+          <t>37,45</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,23; 35,16</t>
+          <t>31,7; 35,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,4; 31,17</t>
+          <t>28,76; 32,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,18; 31,72</t>
+          <t>28,83; 32,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,36; 36,36</t>
+          <t>36,62; 41,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,49; 35,62</t>
+          <t>31,12; 34,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,79; 33,04</t>
+          <t>27,28; 31,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,84; 32,54</t>
+          <t>28,32; 31,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,58; 40,65</t>
+          <t>33,39; 37,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,91; 34,78</t>
+          <t>31,84; 34,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,66; 31,35</t>
+          <t>28,75; 31,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,02; 31,75</t>
+          <t>29,11; 31,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,25; 37,95</t>
+          <t>35,75; 39,34</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33,28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29,42</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30,17</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40,41</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>31,2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>29,34</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>29,49</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37,93</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>33,28</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29,42</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>30,17</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39,35</t>
+          <t>34,79</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,62</t>
+          <t>37,71</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,17; 33,6</t>
+          <t>30,86; 36,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,26; 31,54</t>
+          <t>27,18; 31,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,6; 31,44</t>
+          <t>28,24; 32,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,36; 47,04</t>
+          <t>36,86; 45,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,76; 35,8</t>
+          <t>29,09; 33,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,29; 31,87</t>
+          <t>27,27; 31,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,26; 32,34</t>
+          <t>27,6; 31,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,91; 43,99</t>
+          <t>32,61; 37,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,73; 34,1</t>
+          <t>30,72; 34,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,81; 31,11</t>
+          <t>27,87; 31,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,56; 31,25</t>
+          <t>28,46; 31,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35,89; 43,74</t>
+          <t>35,63; 40,49</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33,32</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30,99</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31,21</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35,9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>30,69</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>30,28</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>30,11</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>33,38</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>33,32</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,99</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31,21</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>35,53</t>
+          <t>34,24</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,49</t>
+          <t>35,07</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,96; 32,57</t>
+          <t>31,18; 35,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,49; 32,66</t>
+          <t>29,14; 33,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,16; 32,41</t>
+          <t>29,26; 33,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,12; 35,93</t>
+          <t>33,55; 38,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,17; 35,75</t>
+          <t>28,94; 32,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,09; 33,12</t>
+          <t>28,32; 32,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,28; 33,41</t>
+          <t>28,1; 32,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,18; 38,24</t>
+          <t>31,99; 36,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,45; 33,37</t>
+          <t>30,59; 33,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,14; 32,16</t>
+          <t>29,26; 32,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,16; 32,18</t>
+          <t>29,25; 32,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,91; 36,31</t>
+          <t>33,4; 36,82</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33,98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30,75</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30,89</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>38,48</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>31,68</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>29,79</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>30,09</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>34,89</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>33,98</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,75</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>30,89</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37,73</t>
+          <t>34,84</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,41</t>
+          <t>36,76</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,67; 32,74</t>
+          <t>32,79; 35,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,74; 30,97</t>
+          <t>29,52; 31,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,11; 31,11</t>
+          <t>29,86; 31,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,3; 38,77</t>
+          <t>36,9; 40,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,76; 35,15</t>
+          <t>30,58; 32,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,68; 32,02</t>
+          <t>28,73; 30,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,84; 31,96</t>
+          <t>29,08; 31,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>36,28; 39,49</t>
+          <t>33,58; 36,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,02; 33,58</t>
+          <t>32,09; 33,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,51; 31,06</t>
+          <t>29,51; 31,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,76; 31,2</t>
+          <t>29,8; 31,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,36; 38,05</t>
+          <t>35,74; 37,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, declarado por progenitor/a (tasa de respuesta: 96,01%)</t>
+          <t>Peso medio, en kilogramos, declarado por madres/padres (tasa de respuesta: 96,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>35,91</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>31,92</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31,56</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38,44</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>31,66</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,48</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,9</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>34,54</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>33,91</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>31,23</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>31,24</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>36,58</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>35.90709636054176</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>31.91708783755909</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>31.55535498994122</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>38.44085959967434</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>31.66207709609607</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>30.4783376112714</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>30.90093011819169</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>34.54346251135737</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>33.91389373846143</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>31.22771680022374</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>31.23755258695391</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>36.57566445775424</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>33,13; 38,77</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>29,35; 34,79</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>29,16; 34,35</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35,23; 41,93</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>29,18; 33,93</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,1; 32,95</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>28,79; 33,33</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32,03; 37,09</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>31,95; 35,88</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>29,36; 33,05</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>29,68; 33,33</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>34,79; 39,04</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>33.13449553602311</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>29.34962903935933</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>29.16444829853284</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>35.23021240160108</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>29.17780596043044</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>28.10076878756948</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>28.79350055439031</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>32.0332091083977</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>31.95433776364492</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>29.35629937863975</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>29.67708493518523</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>34.79105235647516</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>38.77286601186832</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>34.78805779812386</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>34.34689669259878</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>41.92849231130597</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>33.93432604154174</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>32.94879122041041</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>33.32653310667455</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>37.09450929821676</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>35.87857031603126</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>33.04732401537103</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>33.32777725295958</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>39.03634171168071</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>33,68</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>30,69</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>30,71</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>38,92</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>33,08</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>29,18</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>30,01</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35,58</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>33,39</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>29,96</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>30,37</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>37,45</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>31,7; 35,77</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>28,76; 32,78</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>28,83; 32,55</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>36,62; 41,54</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>31,12; 34,88</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>27,28; 31,11</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28,32; 31,9</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>33,39; 37,79</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>31,84; 34,76</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>28,75; 31,46</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>29,11; 31,71</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>35,75; 39,34</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>33.679983092985</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>30.69481923771008</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>30.71127527203768</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>38.91535690160121</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>33.0841528608858</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>29.17677193993993</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>30.00644915200513</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>35.58115477375053</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>33.3930911877967</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>29.96435022890135</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>30.37268856480405</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>37.44547085370733</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>33,28</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>29,42</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>30,17</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>40,41</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31,2</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29,34</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>29,49</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>34,79</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>32,28</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>29,38</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>29,84</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>37,71</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>31.69614938739318</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>28.76496282093206</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>28.83016960063009</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>36.62082746006055</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>31.11811121363367</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>27.2840346029266</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>28.31770330653266</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>33.38957741556481</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>31.83806093695074</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>28.75298297317173</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>29.10831324914393</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>35.74699478839354</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>30,86; 36,05</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>27,18; 31,71</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28,24; 32,49</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>36,86; 45,11</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>29,09; 33,81</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>27,27; 31,54</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>27,6; 31,41</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>32,61; 37,36</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>30,72; 34,02</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>27,87; 31,08</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>28,46; 31,4</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>35,63; 40,49</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>35.77433883909936</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>32.78348163690377</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>32.55210305461379</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>41.535302327079</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>34.88240202931007</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>31.11440764553128</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>31.90110858771986</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>37.79138949085932</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>34.76328831099889</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>31.45551110775767</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>31.71025577977775</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>39.34271109215883</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>33,32</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>30,99</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>31,21</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35,9</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30,69</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,28</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,11</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>34,24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>31,99</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>30,64</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>30,66</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>35,07</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>33.28354036550515</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>29.42111480352295</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>30.17121540597452</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>40.40518572862153</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>31.19932020414273</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>29.33514337403296</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>29.48860256535551</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>34.7890331015558</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>32.27999374064173</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>29.3789658847504</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>29.83502145771581</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>37.70969347837318</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>31,18; 35,68</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>29,14; 33,34</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>29,26; 33,59</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33,55; 38,47</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>28,94; 32,58</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,32; 32,69</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>28,1; 32,28</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>31,99; 36,78</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>30,59; 33,42</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>29,26; 32,29</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>29,25; 32,14</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>33,4; 36,82</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>30.85908003210887</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>27.18059090012849</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>28.2421416113228</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>36.8614370942274</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>29.09085094374068</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>27.26867748670289</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>27.59866806277644</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>32.61358153615417</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>30.72127161544235</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>27.86803123576148</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>28.4565585022852</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>35.62995414299397</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>36.04612580633624</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>31.71062643759802</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>32.48732328923571</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>45.11342170530406</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>33.81225367070419</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>31.54296911312404</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>31.40815909515655</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>37.3593338494952</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>34.02000376953617</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>31.08148785239115</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>31.3981837852158</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>40.49177023491619</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>33.32065469922532</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>30.99414727607163</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>31.2133901004761</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>35.90056287506072</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>30.69093179551719</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>30.28418018771822</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>30.11015238312216</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>34.243087739791</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>31.98542304532428</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>30.63666194849738</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>30.65958404366515</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>35.07351226225779</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>31.18207636884914</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>29.14376146065209</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>29.25966436717916</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>33.55072734431517</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>28.93662165303034</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>28.32492112106794</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>28.10299565286705</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>31.99234434959336</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>30.58965402035131</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>29.26144012095586</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>29.24979524931354</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>33.39966791432287</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>35.67899028223846</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>33.3410553579186</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>33.59009293167219</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>38.47410506736792</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>32.58185558074764</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>32.68740178048815</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>32.2755567927509</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>36.78190180654176</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>33.41891149806433</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>32.29466395112619</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>32.14103482443173</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>36.81820131579633</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>33,98</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>30,75</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>30,89</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>38,48</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>31,68</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>29,79</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>30,09</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>34,84</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>32,86</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>30,28</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>30,5</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>36,76</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>32,79; 35,17</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>29,52; 31,89</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29,86; 31,96</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36,9; 40,17</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>30,58; 32,7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,73; 30,91</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,08; 31,15</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33,58; 36,03</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>32,09; 33,71</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>29,51; 31,15</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29,8; 31,25</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>35,74; 37,88</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>33.97858178118736</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>30.74900930956836</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>30.89386384577849</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>38.4777046442728</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>31.67946562434066</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>29.79499231024989</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>30.09099794967194</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>34.83741900075168</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>32.85958149250187</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>30.2823536765403</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>30.50029104602862</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>36.76007697944866</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>32.78986677199755</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>29.52387587486694</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>29.85555003947752</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>36.90430442148803</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>30.58184131401931</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>28.73098424343596</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>29.07987545762241</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>33.58115039222896</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>32.09322742954793</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>29.51014300913656</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>29.79823078815953</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>35.74211893175089</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>35.16910291854562</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>31.88584827116886</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>31.96246024512977</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>40.1687301002037</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>32.69639658263149</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>30.90687813639867</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>31.14784056787221</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>36.02678730498279</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>33.71374599789781</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>31.15277743867667</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>31.24508485558694</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>37.8790480707251</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
